--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R977cf0bcff8a4d74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R67ed78f0786e432e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8314,7 +8314,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="259">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REslava.ResultFlow</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/REslava.ResultFlow</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/REslava.ResultFlow/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/reslava/nuget-package-reslava-result/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Documentation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-03-18T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F258"/>
+  <x:autoFilter ref="A1:F259"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R67ed78f0786e432e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rfdba123c93ff4d0f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rfdba123c93ff4d0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R23b086481cb74b0e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R23b086481cb74b0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rbec882f64b2e42fe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8346,7 +8346,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="260">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TypedPaths</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/TypedPaths</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/TypedPaths.Generator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/AlexChim1231/TypedPaths/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FilesToCode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-04-01T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F259"/>
+  <x:autoFilter ref="A1:F260"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rbec882f64b2e42fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R180f509a156a420a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8378,7 +8378,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="261">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AssemblyMetadata</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/AssemblyMetadata</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/AssemblyMetadata/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/BenjaminAbt/AssemblyMetadata</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EnhancementProject</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-04-02T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F260"/>
+  <x:autoFilter ref="A1:F261"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R180f509a156a420a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Ra1c0c43c64f348ca"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Ra1c0c43c64f348ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Ra49dd08e4ffa4533"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8410,7 +8410,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="262">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">NLog.Extensions.ThisClass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/NLog.Extensions.ThisClass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/NLog.Extensions.ThisClass/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/trympet/ThisClass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EnhancementClass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-04-03T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F261"/>
+  <x:autoFilter ref="A1:F262"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Ra49dd08e4ffa4533"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rbbfca340cb5c4934"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rbbfca340cb5c4934"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R9db2fc268d3e4681"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8442,7 +8442,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="263">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SvgIconGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/SvgIconGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/SvgIconGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/helluvamatt/SvgIconGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FilesToCode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-04-04T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F262"/>
+  <x:autoFilter ref="A1:F263"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R9db2fc268d3e4681"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rbf13d3e9364940df"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rbf13d3e9364940df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rf310873fb6414a34"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8474,7 +8474,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="264">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TaggedEnum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/TaggedEnum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/TaggedEnum/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/al0rid4l/SixTatami</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-04-05T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F263"/>
+  <x:autoFilter ref="A1:F264"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rf310873fb6414a34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R7f29589930c44737"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R7f29589930c44737"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rdcfb42b4f4af44c4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8506,7 +8506,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="265">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Najlot.Audit.SourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Najlot.Audit.SourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Najlot.Audit.SourceGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/najlot/Audit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Audit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-04-06T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F264"/>
+  <x:autoFilter ref="A1:F265"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rdcfb42b4f4af44c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R6f76ad5933e84fca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8538,7 +8538,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="266">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">lomapper</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/loMapper</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/lomapper/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/jdtoon/lomapper</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Serializer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-04-07T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F265"/>
+  <x:autoFilter ref="A1:F266"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R6f76ad5933e84fca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R94468bfc30b148c7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R94468bfc30b148c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R02d4923fe6744e2c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8561,7 +8561,7 @@
       </x:c>
       <x:c r="E" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Serializer</x:t>
+          <x:t xml:space="preserve">Mapper</x:t>
         </x:is>
       </x:c>
       <x:c r="F" s="4" t="inlineStr">

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R02d4923fe6744e2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rca83f5185b674689"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rca83f5185b674689"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Reaff073d2ca04612"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8546,7 +8546,7 @@
       </x:c>
       <x:c r="B" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/loMapper</x:t>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/lomapper</x:t>
         </x:is>
       </x:c>
       <x:c r="C" s="4" t="inlineStr">

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Reaff073d2ca04612"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R3a63bd02ad1e4576"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8570,7 +8570,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="267">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Aigamo.MatchGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Aigamo.MatchGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Aigamo.MatchGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/ycanardeau/MatchGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-04-05T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F266"/>
+  <x:autoFilter ref="A1:F267"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R3a63bd02ad1e4576"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R46b4c56b121445ed"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R46b4c56b121445ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rb3e6965dd6d64a87"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8598,7 +8598,7 @@
       </x:c>
       <x:c r="F" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">2026-04-05T00:00:00</x:t>
+          <x:t xml:space="preserve">2026-04-08T00:00:00</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rb3e6965dd6d64a87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Ree4d1f192e624082"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8602,7 +8602,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="268">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Maestria.TypeProviders</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Maestria.TypeProviders</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Maestria.TypeProviders/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/MaestriaNet/TypeProviders</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FilesToCode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-04-09T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F267"/>
+  <x:autoFilter ref="A1:F268"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Ree4d1f192e624082"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rda79deddd84f4e4f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rda79deddd84f4e4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R475e4aaa4c874e98"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8634,7 +8634,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="269">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GenerateDispose</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/GenerateDispose</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/GenerateDispose/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/ItaiTzur76/GenerateDispose</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Disposer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-05-13T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F268"/>
+  <x:autoFilter ref="A1:F269"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R475e4aaa4c874e98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rad85af1583de4861"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8666,7 +8666,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="270">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LinkDotNet.Enumeration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/LinkDotNet.Enumeration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/LinkDotNet.Enumeration/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/linkdotnet/Enumeration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-05-14T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F269"/>
+  <x:autoFilter ref="A1:F270"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rad85af1583de4861"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R3e904e2a4d5044b3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R3e904e2a4d5044b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R6b8818e3b40d4fc3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8698,7 +8698,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="271">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AssemblyMetadata.Generators</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/AssemblyMetadata.Generators</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/AssemblyMetadata.Generators/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/loresoft/AssemblyMetadata.Generators</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EnhancementProject</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-04-02T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F270"/>
+  <x:autoFilter ref="A1:F271"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R6b8818e3b40d4fc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R5bcdcd3ab6634ec7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8726,11 +8726,43 @@
       </x:c>
       <x:c r="F" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">2026-04-02T00:00:00</x:t>
+          <x:t xml:space="preserve">2026-05-15T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TypedStateBuilder.Generator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/TypedStateBuilder.Generator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/TypedStateBuilder.Generator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Georgiy-Petrov/TypedStateBuilder.Generator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Builder</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-05-16T00:00:00</x:t>
         </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F271"/>
+  <x:autoFilter ref="A1:F272"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R5bcdcd3ab6634ec7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R45a3723c3c4f4455"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8762,7 +8762,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="273">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AlephMapper</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/AlephMapper</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/AlephMapper/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Raffinert/AlephMapper</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Database</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-06-29T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F272"/>
+  <x:autoFilter ref="A1:F273"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R45a3723c3c4f4455"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rd4de5096a6b247a7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8794,7 +8794,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="274">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ScottEncodingGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/ScottEncodingGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/ScottEncodingGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Georgiy-Petrov/ScottEncodingGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FunctionalProgramming</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-06-30T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F273"/>
+  <x:autoFilter ref="A1:F274"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rd4de5096a6b247a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R5affafb46fa642df"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8826,7 +8826,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="275">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Dirge</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Dirge</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Dirge/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/IkuzakIkuzok/Dirge</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Disposer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-07-01T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F274"/>
+  <x:autoFilter ref="A1:F275"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R5affafb46fa642df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R7b9fc0622e7545cc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R7b9fc0622e7545cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R032f2e6a6ff14322"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8858,7 +8858,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="276">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Porticle.Enumly</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Porticle.Enumly</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Porticle.Enumly/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Machibuse/Porticle.Enumly</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-07-02T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F275"/>
+  <x:autoFilter ref="A1:F276"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R032f2e6a6ff14322"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R4226b86ca44649bb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8890,7 +8890,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="277">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TinyBDD.MSTest</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/TinyBDD.MSTest</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/TinyBDD.MSTest/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/JerrettDavis/TinyBDD</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tests</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-07-03T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F276"/>
+  <x:autoFilter ref="A1:F277"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R4226b86ca44649bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R62b522362bcd4214"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8922,7 +8922,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="278">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Bennewitz.Ninja.AutoVersioning</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Bennewitz.Ninja.AutoVersioning</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Bennewitz.Ninja.AutoVersioning/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/JanusMael/Bennewitz.Ninja.AutoVersioning</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EnhancementProject</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-07-04T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F277"/>
+  <x:autoFilter ref="A1:F278"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R62b522362bcd4214"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R9a6b93cc5d0249a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6065,34 +6065,2050 @@
       </x:c>
       <x:c r="E" s="4" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">EntityFramework</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-02-19T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">StepwiseBuilderGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/StepwiseBuilderGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/StepwiseBuilderGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Georgiy-Petrov/StepwiseBuilderGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Builder</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-03-23T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MemberAccessor</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/MemberAccessor</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/BunnyTail.MemberAccessor/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/usausa/member-accessor-generator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EnhancementClass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-03-24T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PMart.Enumeration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/PMart.Enumeration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/PMart.Enumeration.Generator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/p-martinho/Enumeration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-03-25T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">rscg_demeter</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/rscg_demeter</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/rscg_demeter/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/ignatandrei/rscg_demeter/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FunctionalProgramming</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-03-26T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">immediate.apis</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Immediate.APIs</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/immediate.apis/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/immediateplatform/immediate.apis</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">API</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-03-27T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">NativeObjects</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/NativeObjects</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/NativeObjects/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/kevingosse/NativeObjects</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">WinAPI</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-03-28T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">zlinq</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/zlinq</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/ZLinq.DropInGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Cysharp/ZLinq</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Linq</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-07-02T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Comparison</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Comparison</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/ReflectionIT.ComparisonOperatorsGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/sonnemaf/ReflectionIT.ComparisonOperatorsGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EnhancementClass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-05-25T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ArgumentParsing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/ArgumentParsing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/ArgumentParsing/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/DoctorKrolic/ArgumentParsing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CommandLine</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-07-01T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BunnyTailServiceRegistration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/BunnyTailServiceRegistration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/BunnyTail.ServiceRegistration/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/usausa/service-registration-generator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DependencyInjection</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-07-02T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DimonSmart.BuilderGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/DimonSmart.BuilderGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/DimonSmart.BuilderGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/DimonSmart/BuilderGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Builder</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-07-03T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SuperFluid</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/SuperFluid</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/SuperFluid/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/hughesjs/SuperFluid</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">StateMachine</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-07-04T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Figgle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Figgle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Figgle.Generator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/drewnoakes/figgle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Console</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-07-05T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Strings.ResourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Strings.ResourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Strings.ResourceGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/biggik/Strings.ResourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FilesToCode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-07-06T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">jos.enumeration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Jos.Enumeration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/jos.enumeration/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/joseftw/jos.enumeration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-07-20T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tortuga.Shipwright</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Tortuga.Shipwright</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Tortuga.Shipwright/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/TortugaResearch/Tortuga.Shipwright</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Templating</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-07-21T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">InlineComposition</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/InlineComposition</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/InlineComposition/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/BlackWhiteYoshi/InlineComposition</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Templating</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-07-22T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="206">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Flaggen</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Flaggen</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Flaggen/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/ricardoboss/Flaggen</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-07-23T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ShadowWriterBuilder</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/ShadowWriterBuilder</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/ShadowWriter/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/StefanStolz/ShadowWriter</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Builder</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-07-24T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AutoInterface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/AutoInterface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/AutoInterface/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/BlackWhiteYoshi/AutoInterface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-07-25T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AsyncIt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/AsyncIt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/AsyncIt/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/oleg-shilo/AsyncIt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Async</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-07-26T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ShadowWriterProjectInfo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/ShadowWriterProjectInfo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/ShadowWriter/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/StefanStolz/ShadowWriter</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EnhancementProject</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-07-27T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AssemblyVersionInfo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/AssemblyVersionInfo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/AssemblyVersionInfo/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/BlackWhiteYoshi/AssemblyVersionInfo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EnhancementProject</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-07-28T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ShadowWriterNullobjects</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/ShadowWriterNullobjects</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/ShadowWriter/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/StefanStolz/ShadowWriter</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-07-29T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">StackXML</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/StackXML</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/StackXML/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/ZingBallyhoo/StackXML</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Serializer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-08-01T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Blazor.TSRuntime</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Blazor.TSRuntime</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Blazor.TSRuntime/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/BlackWhiteYoshi/Blazor.TSRuntime</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Blazor</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-08-02T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Genbox.FastEnum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Genbox.FastEnum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Genbox.FastEnum/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Genbox/FastEnum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-08-03T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BadIdeas.Icons.FontAwesome</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/BadIdeas.Icons.FontAwesome</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/BadIdeas.Icons.FontAwesome/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/phil-scott-78/Icons/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Blazor</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-08-03T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SG4MVC</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/SG4MVC</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/SG4MVC/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/SG4MVC/SG4MVC</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MVC</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-08-04T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EnumsEnhanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/EnumsEnhanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/EnumsEnhanced/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/snowberry-software/EnumsEnhanced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-08-05T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Nino</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Nino</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Nino/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/JasonXuDeveloper/Nino</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Serializer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-08-06T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SKPromptGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/SKPromptGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/SKPromptGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/CharlieDigital/SKPromptGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AI</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-08-07T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">NFH.FileEmbed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/NFH.FileEmbed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/NFH.FileEmbed/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/SirCxyrtyx/FileEmbed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FilesToCode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-08-08T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RxSourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/RxSourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/RxSourceGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Zalutskii/Reactive-Extensions-event-generator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RX</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-08-09T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Finch.Generators</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Finch.Generators</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Finch.Generators/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/ivmazurenko/finch</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">Database</x:t>
         </x:is>
       </x:c>
       <x:c r="F" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">2025-02-19T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="189">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">StepwiseBuilderGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/StepwiseBuilderGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/StepwiseBuilderGenerator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/Georgiy-Petrov/StepwiseBuilderGenerator</x:t>
+          <x:t xml:space="preserve">2025-08-10T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">JinShil.MixinSourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/JinShil.MixinSourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/JinShil.MixinSourceGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/JinShil/JinShil.MixinSourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Mixin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-08-11T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FactoryGenerator.Abstractions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/FactoryGenerator.Abstractions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/FactoryGenerator.Abstractions/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/ivmazurenko/factory-generator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DependencyInjection</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-08-12T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Schema</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Schema</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Schema/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/MeltyPlayer/Schema</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Serializer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-08-13T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">requiredenum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/requiredenum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/requiredenum/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/emptycoder/RequiredEnum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-08-14T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">UtilityVerse.Copy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/UtilityVerse.Copy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/UtilityVerse.Copy/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/purkayasta/TheUtilityVerse</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Clone</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-08-15T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">mvvmgen</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/mvvmgen</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/mvvmgen/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/thomasclaudiushuber/mvvmgen</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MVVM</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-08-16T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Facet</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Facet</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Facet/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Tim-Maes/Facet/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Mapper</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-08-17T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unflat</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Unflat</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Unflat/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/pstlnce/unflat</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Database</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-08-18T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">kli.Localize</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/kli.Localize</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/kli.Localize/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/kl1mm/localize</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FilesToCode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-10-01T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ConsoleAppFramework</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/ConsoleAppFramework</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/ConsoleAppFramework/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Cysharp/ConsoleAppFramework</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CommandLine</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-10-02T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">VYaml</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Vyaml</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/VYaml/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/hadashiA/VYaml</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Serializer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-10-03T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RapidEnum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/RapidEnum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/RapidEnum/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/hanachiru/RapidEnum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-10-04T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Csvcsharp</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/CsvCsharp</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Csvcsharp/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/nuskey8/Csv-CSharp</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Serializer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-10-05T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">validly</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Validly</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/validly/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Hookyns/validly</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Validator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-10-06T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="238">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Program</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Program</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Microsoft.AspNetCore.OpenApi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/dotnet/aspnetcore/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EnhancementClass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-11-06T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TeCLI</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/TeCLI</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/TeCLI/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/tyevco/TeCLI</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CommandLine</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-11-07T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="240">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TUnit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/TUnit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/TUnit/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/thomhurst/TUnit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tests</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-11-08T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="241">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">XmlCommentGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/XmlCommentGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Microsoft.AspNetCore.OpenApi/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/dotnet/dotnet/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">API</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-11-09T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="242">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RSCG_MCP2OpenAPI</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/RSCG_MCP2OpenAPI</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/RSCG_MCP2OpenAPI/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/ignatandrei/RSCG_OpenApi2MCP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MCP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-11-11T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DecoratorGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/DecoratorGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/DecoratorGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/CodingFlow/decorator-generator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Decorator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-11-13T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RSCG_MCP2File</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/RSCG_MCP2File</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/RSCG_MCP2File/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/ignatandrei/RSCG_OpenApi2MCP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MCP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-11-15T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BoolParameterGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/BoolParameterGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/BoolParameterGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/9swampy/BoolEnumGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Bool</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-12-11T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Monify</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Monify</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Monify/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/MooVC/monify</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PrimitiveObsession</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-12-12T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Imposter</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Imposter</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Imposter/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/themidnightgospel/Imposter</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tests</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-12-13T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BlazorOcticons</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/BlazorOcticons</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/BlazorOcticons/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/BlazorOcticons/BlazorOcticons</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Blazor</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-12-14T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docopt.net</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/docopt.net</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/docopt.net/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/docopt/docopt.net</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CommandLine</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-12-15T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Silhouette</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Silhouette</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Silhouette/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/kevingosse/Silhouette</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Profiler</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-12-16T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Facet.Search</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Facet.Search</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Facet.Search/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Tim-Maes/Facet.Search</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Database</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2025-12-17T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">OrderedBuildersGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/OrderedBuildersGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/OrderedBuildersGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Georgiy-Petrov/OrderedBuildersGenerator</x:t>
         </x:is>
       </x:c>
       <x:c r="E" s="4" t="inlineStr">
@@ -6102,29 +8118,189 @@
       </x:c>
       <x:c r="F" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">2025-03-23T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="190">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MemberAccessor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/MemberAccessor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/BunnyTail.MemberAccessor/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/usausa/member-accessor-generator</x:t>
+          <x:t xml:space="preserve">2025-12-18T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RSCG_idempotency</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/RSCG_idempotency</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/RSCG_idempotency/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/ignatandrei/RSCG_idempotency</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Idempotency</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-01-28T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FastCloner</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/FastCloner</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/FastCloner/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/lofcz/FastCloner/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Clone</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-02-01T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ErrorOrX</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/ErrorOrX</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/ErrorOrX/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/ANcpLua/ErrorOrX</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">API</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-02-02T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">KnockOff</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/KnockOff</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/KnockOff/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/NeatooDotNet/KnockOff</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tests</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-02-13T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Sundew.DiscriminatedUnions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Sundew.DiscriminatedUnions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Sundew.DiscriminatedUnions/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/sundews/Sundew.DiscriminatedUnions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FunctionalProgramming</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-02-14T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pekspro.DataAnnotationValuesExtractor</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Pekspro.DataAnnotationValuesExtractor</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Pekspro.DataAnnotationValuesExtractor/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/pekspro/DataAnnotationValuesExtractor</x:t>
         </x:is>
       </x:c>
       <x:c r="E" s="4" t="inlineStr">
@@ -6134,29 +8310,189 @@
       </x:c>
       <x:c r="F" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">2025-03-24T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="191">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PMart.Enumeration</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/PMart.Enumeration</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/PMart.Enumeration.Generator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/p-martinho/Enumeration</x:t>
+          <x:t xml:space="preserve">2026-02-15T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="259">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REslava.ResultFlow</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/REslava.ResultFlow</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/REslava.ResultFlow/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/reslava/nuget-package-reslava-result/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Documentation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-03-18T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="260">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TypedPaths</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/TypedPaths</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/TypedPaths.Generator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/AlexChim1231/TypedPaths/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FilesToCode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-04-01T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="261">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AssemblyMetadata</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/AssemblyMetadata</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/AssemblyMetadata/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/BenjaminAbt/AssemblyMetadata</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EnhancementProject</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-04-02T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">NLog.Extensions.ThisClass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/NLog.Extensions.ThisClass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/NLog.Extensions.ThisClass/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/trympet/ThisClass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EnhancementClass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-04-03T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="263">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SvgIconGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/SvgIconGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/SvgIconGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/helluvamatt/SvgIconGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FilesToCode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-04-04T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="264">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TaggedEnum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/TaggedEnum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/TaggedEnum/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/al0rid4l/SixTatami</x:t>
         </x:is>
       </x:c>
       <x:c r="E" s="4" t="inlineStr">
@@ -6166,29 +8502,317 @@
       </x:c>
       <x:c r="F" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">2025-03-25T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="192">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">rscg_demeter</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/rscg_demeter</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/rscg_demeter/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/ignatandrei/rscg_demeter/</x:t>
+          <x:t xml:space="preserve">2026-04-05T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="265">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Najlot.Audit.SourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Najlot.Audit.SourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Najlot.Audit.SourceGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/najlot/Audit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Audit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-04-06T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">lomapper</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/lomapper</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/lomapper/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/jdtoon/lomapper</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Mapper</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-04-07T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Aigamo.MatchGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Aigamo.MatchGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Aigamo.MatchGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/ycanardeau/MatchGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-04-08T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Maestria.TypeProviders</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Maestria.TypeProviders</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Maestria.TypeProviders/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/MaestriaNet/TypeProviders</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FilesToCode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-04-09T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="269">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GenerateDispose</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/GenerateDispose</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/GenerateDispose/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/ItaiTzur76/GenerateDispose</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Disposer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-05-13T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="270">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LinkDotNet.Enumeration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/LinkDotNet.Enumeration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/LinkDotNet.Enumeration/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/linkdotnet/Enumeration</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-05-14T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="271">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AssemblyMetadata.Generators</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/AssemblyMetadata.Generators</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/AssemblyMetadata.Generators/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/loresoft/AssemblyMetadata.Generators</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EnhancementProject</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-05-15T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TypedStateBuilder.Generator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/TypedStateBuilder.Generator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/TypedStateBuilder.Generator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Georgiy-Petrov/TypedStateBuilder.Generator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Builder</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-05-16T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AlephMapper</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/AlephMapper</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/AlephMapper/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Raffinert/AlephMapper</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Database</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-06-29T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="274">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ScottEncodingGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/ScottEncodingGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/ScottEncodingGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Georgiy-Petrov/ScottEncodingGenerator</x:t>
         </x:is>
       </x:c>
       <x:c r="E" s="4" t="inlineStr">
@@ -6198,349 +8822,61 @@
       </x:c>
       <x:c r="F" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">2025-03-26T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="193">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">immediate.apis</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Immediate.APIs</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/immediate.apis/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/immediateplatform/immediate.apis</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">API</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-03-27T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="194">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">NativeObjects</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/NativeObjects</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/NativeObjects/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/kevingosse/NativeObjects</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">WinAPI</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-03-28T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="195">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">zlinq</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/zlinq</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/ZLinq.DropInGenerator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/Cysharp/ZLinq</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Linq</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-07-02T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="196">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Comparison</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Comparison</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/ReflectionIT.ComparisonOperatorsGenerator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/sonnemaf/ReflectionIT.ComparisonOperatorsGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EnhancementClass</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-05-25T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="197">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ArgumentParsing</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/ArgumentParsing</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/ArgumentParsing/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/DoctorKrolic/ArgumentParsing</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CommandLine</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-07-01T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="198">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BunnyTailServiceRegistration</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/BunnyTailServiceRegistration</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/BunnyTail.ServiceRegistration/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/usausa/service-registration-generator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DependencyInjection</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-07-02T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="199">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DimonSmart.BuilderGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/DimonSmart.BuilderGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/DimonSmart.BuilderGenerator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/DimonSmart/BuilderGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Builder</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-07-03T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="200">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SuperFluid</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/SuperFluid</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/SuperFluid/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/hughesjs/SuperFluid</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">StateMachine</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-07-04T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="201">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Figgle</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Figgle</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Figgle.Generator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/drewnoakes/figgle</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Console</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-07-05T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="202">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Strings.ResourceGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Strings.ResourceGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Strings.ResourceGenerator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/biggik/Strings.ResourceGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FilesToCode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-07-06T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="203">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">jos.enumeration</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Jos.Enumeration</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/jos.enumeration/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/joseftw/jos.enumeration</x:t>
+          <x:t xml:space="preserve">2026-06-30T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="275">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Dirge</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Dirge</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Dirge/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/IkuzakIkuzok/Dirge</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Disposer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-07-01T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Porticle.Enumly</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Porticle.Enumly</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Porticle.Enumly/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Machibuse/Porticle.Enumly</x:t>
         </x:is>
       </x:c>
       <x:c r="E" s="4" t="inlineStr">
@@ -6550,221 +8886,61 @@
       </x:c>
       <x:c r="F" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">2025-07-20T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="204">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tortuga.Shipwright</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Tortuga.Shipwright</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Tortuga.Shipwright/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/TortugaResearch/Tortuga.Shipwright</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Templating</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-07-21T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="205">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">InlineComposition</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/InlineComposition</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/InlineComposition/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/BlackWhiteYoshi/InlineComposition</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Templating</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-07-22T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="206">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Flaggen</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Flaggen</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Flaggen/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/ricardoboss/Flaggen</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Enum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-07-23T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="207">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ShadowWriterBuilder</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/ShadowWriterBuilder</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/ShadowWriter/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/StefanStolz/ShadowWriter</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Builder</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-07-24T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="208">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AutoInterface</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/AutoInterface</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/AutoInterface/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/BlackWhiteYoshi/AutoInterface</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Interface</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-07-25T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="209">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AsyncIt</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/AsyncIt</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/AsyncIt/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/oleg-shilo/AsyncIt</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Async</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-07-26T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="210">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ShadowWriterProjectInfo</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/ShadowWriterProjectInfo</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/ShadowWriter/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/StefanStolz/ShadowWriter</x:t>
+          <x:t xml:space="preserve">2026-07-02T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TinyBDD.MSTest</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/TinyBDD.MSTest</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/TinyBDD.MSTest/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/JerrettDavis/TinyBDD</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tests</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-07-03T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Bennewitz.Ninja.AutoVersioning</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Bennewitz.Ninja.AutoVersioning</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Bennewitz.Ninja.AutoVersioning/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/JanusMael/Bennewitz.Ninja.AutoVersioning</x:t>
         </x:is>
       </x:c>
       <x:c r="E" s="4" t="inlineStr">
@@ -6774,226 +8950,34 @@
       </x:c>
       <x:c r="F" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">2025-07-27T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="211">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AssemblyVersionInfo</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/AssemblyVersionInfo</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/AssemblyVersionInfo/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/BlackWhiteYoshi/AssemblyVersionInfo</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EnhancementProject</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-07-28T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="212">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ShadowWriterNullobjects</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/ShadowWriterNullobjects</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/ShadowWriter/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/StefanStolz/ShadowWriter</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Interface</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-07-29T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="213">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">StackXML</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/StackXML</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/StackXML/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/ZingBallyhoo/StackXML</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Serializer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-08-01T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="214">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Blazor.TSRuntime</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Blazor.TSRuntime</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Blazor.TSRuntime/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/BlackWhiteYoshi/Blazor.TSRuntime</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Blazor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-08-02T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="215">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Genbox.FastEnum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Genbox.FastEnum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Genbox.FastEnum/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/Genbox/FastEnum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Enum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-08-03T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="216">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BadIdeas.Icons.FontAwesome</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/BadIdeas.Icons.FontAwesome</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/BadIdeas.Icons.FontAwesome/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/phil-scott-78/Icons/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Blazor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-08-03T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="217">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SG4MVC</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/SG4MVC</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/SG4MVC/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/SG4MVC/SG4MVC</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MVC</x:t>
+          <x:t xml:space="preserve">2026-07-04T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Atulin.AutoDbSet</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Atulin.AutoDbSet</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Atulin.AutoDbSet/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/Atulin/AutoDbSet</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EntityFramework</x:t>
         </x:is>
       </x:c>
       <x:c r="F" s="4" t="inlineStr">
@@ -7002,1959 +8986,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="218">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EnumsEnhanced</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/EnumsEnhanced</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/EnumsEnhanced/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/snowberry-software/EnumsEnhanced</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Enum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-08-05T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="219">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Nino</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Nino</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Nino/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/JasonXuDeveloper/Nino</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Serializer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-08-06T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="220">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SKPromptGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/SKPromptGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/SKPromptGenerator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/CharlieDigital/SKPromptGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AI</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-08-07T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="221">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">NFH.FileEmbed</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/NFH.FileEmbed</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/NFH.FileEmbed/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/SirCxyrtyx/FileEmbed</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FilesToCode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-08-08T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="222">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RxSourceGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/RxSourceGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/RxSourceGenerator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/Zalutskii/Reactive-Extensions-event-generator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-08-09T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="223">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Finch.Generators</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Finch.Generators</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Finch.Generators/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/ivmazurenko/finch</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Database</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-08-10T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="224">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">JinShil.MixinSourceGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/JinShil.MixinSourceGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/JinShil.MixinSourceGenerator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/JinShil/JinShil.MixinSourceGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mixin</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-08-11T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="225">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FactoryGenerator.Abstractions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/FactoryGenerator.Abstractions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/FactoryGenerator.Abstractions/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/ivmazurenko/factory-generator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DependencyInjection</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-08-12T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="226">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Schema</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Schema</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Schema/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/MeltyPlayer/Schema</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Serializer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-08-13T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="227">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">requiredenum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/requiredenum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/requiredenum/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/emptycoder/RequiredEnum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Enum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-08-14T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="228">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">UtilityVerse.Copy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/UtilityVerse.Copy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/UtilityVerse.Copy/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/purkayasta/TheUtilityVerse</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Clone</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-08-15T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="229">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">mvvmgen</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/mvvmgen</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/mvvmgen/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/thomasclaudiushuber/mvvmgen</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MVVM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-08-16T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="230">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Facet</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Facet</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Facet/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/Tim-Maes/Facet/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mapper</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-08-17T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="231">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Unflat</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Unflat</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Unflat/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/pstlnce/unflat</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Database</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-08-18T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="232">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">kli.Localize</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/kli.Localize</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/kli.Localize/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/kl1mm/localize</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FilesToCode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-10-01T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="233">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ConsoleAppFramework</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/ConsoleAppFramework</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/ConsoleAppFramework/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/Cysharp/ConsoleAppFramework</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CommandLine</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-10-02T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="234">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">VYaml</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Vyaml</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/VYaml/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/hadashiA/VYaml</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Serializer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-10-03T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="235">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RapidEnum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/RapidEnum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/RapidEnum/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/hanachiru/RapidEnum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Enum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-10-04T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="236">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Csvcsharp</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/CsvCsharp</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Csvcsharp/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/nuskey8/Csv-CSharp</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Serializer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-10-05T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="237">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">validly</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Validly</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/validly/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/Hookyns/validly</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Validator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-10-06T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="238">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Program</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Program</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Microsoft.AspNetCore.OpenApi</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/dotnet/aspnetcore/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EnhancementClass</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-11-06T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="239">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TeCLI</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/TeCLI</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/TeCLI/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/tyevco/TeCLI</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CommandLine</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-11-07T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="240">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TUnit</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/TUnit</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/TUnit/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/thomhurst/TUnit</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tests</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-11-08T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="241">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">XmlCommentGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/XmlCommentGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Microsoft.AspNetCore.OpenApi/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/dotnet/dotnet/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">API</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-11-09T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="242">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RSCG_MCP2OpenAPI</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/RSCG_MCP2OpenAPI</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/RSCG_MCP2OpenAPI/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/ignatandrei/RSCG_OpenApi2MCP</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MCP</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-11-11T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="243">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DecoratorGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/DecoratorGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/DecoratorGenerator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/CodingFlow/decorator-generator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Decorator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-11-13T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="244">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RSCG_MCP2File</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/RSCG_MCP2File</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/RSCG_MCP2File/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/ignatandrei/RSCG_OpenApi2MCP</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MCP</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-11-15T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="245">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BoolParameterGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/BoolParameterGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/BoolParameterGenerator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/9swampy/BoolEnumGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bool</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-12-11T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="246">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Monify</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Monify</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Monify/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/MooVC/monify</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PrimitiveObsession</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-12-12T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="247">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Imposter</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Imposter</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Imposter/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/themidnightgospel/Imposter</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tests</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-12-13T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="248">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BlazorOcticons</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/BlazorOcticons</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/BlazorOcticons/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/BlazorOcticons/BlazorOcticons</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Blazor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-12-14T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="249">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">docopt.net</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/docopt.net</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/docopt.net/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/docopt/docopt.net</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CommandLine</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-12-15T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="250">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Silhouette</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Silhouette</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Silhouette/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/kevingosse/Silhouette</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Profiler</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-12-16T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="251">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Facet.Search</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Facet.Search</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Facet.Search/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/Tim-Maes/Facet.Search</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Database</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-12-17T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="252">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">OrderedBuildersGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/OrderedBuildersGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/OrderedBuildersGenerator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/Georgiy-Petrov/OrderedBuildersGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Builder</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2025-12-18T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="253">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RSCG_idempotency</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/RSCG_idempotency</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/RSCG_idempotency/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/ignatandrei/RSCG_idempotency</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Idempotency</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-01-28T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="254">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FastCloner</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/FastCloner</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/FastCloner/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/lofcz/FastCloner/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Clone</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-02-01T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="255">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ErrorOrX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/ErrorOrX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/ErrorOrX/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/ANcpLua/ErrorOrX</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">API</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-02-02T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="256">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">KnockOff</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/KnockOff</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/KnockOff/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/NeatooDotNet/KnockOff</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tests</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-02-13T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="257">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Sundew.DiscriminatedUnions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Sundew.DiscriminatedUnions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Sundew.DiscriminatedUnions/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/sundews/Sundew.DiscriminatedUnions</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FunctionalProgramming</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-02-14T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="258">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pekspro.DataAnnotationValuesExtractor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Pekspro.DataAnnotationValuesExtractor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Pekspro.DataAnnotationValuesExtractor/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/pekspro/DataAnnotationValuesExtractor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EnhancementClass</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-02-15T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="259">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REslava.ResultFlow</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/REslava.ResultFlow</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/REslava.ResultFlow/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/reslava/nuget-package-reslava-result/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Documentation</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-03-18T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="260">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TypedPaths</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/TypedPaths</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/TypedPaths.Generator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/AlexChim1231/TypedPaths/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FilesToCode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-04-01T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="261">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AssemblyMetadata</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/AssemblyMetadata</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/AssemblyMetadata/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/BenjaminAbt/AssemblyMetadata</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EnhancementProject</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-04-02T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="262">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">NLog.Extensions.ThisClass</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/NLog.Extensions.ThisClass</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/NLog.Extensions.ThisClass/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/trympet/ThisClass</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EnhancementClass</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-04-03T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="263">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SvgIconGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/SvgIconGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/SvgIconGenerator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/helluvamatt/SvgIconGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FilesToCode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-04-04T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="264">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TaggedEnum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/TaggedEnum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/TaggedEnum/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/al0rid4l/SixTatami</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Enum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-04-05T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="265">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Najlot.Audit.SourceGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Najlot.Audit.SourceGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Najlot.Audit.SourceGenerator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/najlot/Audit</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Audit</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-04-06T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="266">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">lomapper</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/lomapper</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/lomapper/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/jdtoon/lomapper</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mapper</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-04-07T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="267">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Aigamo.MatchGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Aigamo.MatchGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Aigamo.MatchGenerator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/ycanardeau/MatchGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Enum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-04-08T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="268">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Maestria.TypeProviders</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Maestria.TypeProviders</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Maestria.TypeProviders/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/MaestriaNet/TypeProviders</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FilesToCode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-04-09T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="269">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GenerateDispose</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/GenerateDispose</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/GenerateDispose/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/ItaiTzur76/GenerateDispose</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Disposer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-05-13T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="270">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">LinkDotNet.Enumeration</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/LinkDotNet.Enumeration</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/LinkDotNet.Enumeration/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/linkdotnet/Enumeration</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Enum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-05-14T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="271">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AssemblyMetadata.Generators</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/AssemblyMetadata.Generators</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/AssemblyMetadata.Generators/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/loresoft/AssemblyMetadata.Generators</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EnhancementProject</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-05-15T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="272">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TypedStateBuilder.Generator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/TypedStateBuilder.Generator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/TypedStateBuilder.Generator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/Georgiy-Petrov/TypedStateBuilder.Generator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Builder</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-05-16T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="273">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AlephMapper</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/AlephMapper</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/AlephMapper/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/Raffinert/AlephMapper</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Database</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-06-29T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="274">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ScottEncodingGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/ScottEncodingGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/ScottEncodingGenerator/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/Georgiy-Petrov/ScottEncodingGenerator</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FunctionalProgramming</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-06-30T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="275">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dirge</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Dirge</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Dirge/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/IkuzakIkuzok/Dirge</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Disposer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-07-01T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="276">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Porticle.Enumly</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Porticle.Enumly</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Porticle.Enumly/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/Machibuse/Porticle.Enumly</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Enum</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-07-02T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="277">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TinyBDD.MSTest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/TinyBDD.MSTest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/TinyBDD.MSTest/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/JerrettDavis/TinyBDD</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Tests</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-07-03T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="278">
-      <x:c r="A" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bennewitz.Ninja.AutoVersioning</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Bennewitz.Ninja.AutoVersioning</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://www.nuget.org/packages/Bennewitz.Ninja.AutoVersioning/</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://github.com/JanusMael/Bennewitz.Ninja.AutoVersioning</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EnhancementProject</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-07-04T00:00:00</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F278"/>
+  <x:autoFilter ref="A1:F279"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R9a6b93cc5d0249a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R6652148e48c44466"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8982,11 +8982,43 @@
       </x:c>
       <x:c r="F" s="4" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">2025-08-04T00:00:00</x:t>
+          <x:t xml:space="preserve">2026-08-18T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ReflectionIT.DisposeGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/ReflectionIT.DisposeGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/ReflectionIT.DisposeGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/sonnemaf/ReflectionIT.DisposeGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Disposer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-08-19T00:00:00</x:t>
         </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F279"/>
+  <x:autoFilter ref="A1:F280"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R6652148e48c44466"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R81229a0617cb4f90"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9018,7 +9018,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="281">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">serde</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/serde</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/serde/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/serdedotnet/serde</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Serializer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-08-20T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F280"/>
+  <x:autoFilter ref="A1:F281"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R81229a0617cb4f90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rf6f751e73bcb4923"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rf6f751e73bcb4923"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Re89dd283222c40ed"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9050,7 +9050,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="282">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EndpointHelpers</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/EndpointHelpers</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/EndpointHelpers/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/gumbarros/EndpointHelpers</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MVC</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-08-21T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F281"/>
+  <x:autoFilter ref="A1:F282"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Re89dd283222c40ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R480f485729474974"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R480f485729474974"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R8d6cbf58ad1542b6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R8d6cbf58ad1542b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R8d8dea907a444660"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9082,7 +9082,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="283">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Clap.Net</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Clap.Net</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Clap.Net/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/simon-curtis/Clap.Net</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CommandLine</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-08-22T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F282"/>
+  <x:autoFilter ref="A1:F283"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R8d8dea907a444660"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R3a046957179f4e06"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R3a046957179f4e06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R593193b1ab6b49d4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9114,7 +9114,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="284">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IncrementalSourceGenerator.BuilderPattern</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/IncrementalSourceGenerator.BuilderPattern</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/IncrementalSourceGenerator.BuilderPattern/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/MartinBarrettNielsen11/Incremental-source-generator-builder-pattern</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Builder</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-08-23T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F283"/>
+  <x:autoFilter ref="A1:F284"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R593193b1ab6b49d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R3831dc318c5d4995"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9146,7 +9146,71 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="285">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pinecone.TypedPath</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Pinecone.TypedPath</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Pinecone.TypedPath/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/nickpinecone/typed-path</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FilesToCode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-08-24T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="286">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PropertyResolvers</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/PropertyResolvers</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/PropertyResolvers/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/tombiddulph/PropertyResolvers</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EnhancementProject</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-08-26T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F284"/>
+  <x:autoFilter ref="A1:F286"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R3831dc318c5d4995"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rc53fc90b01e84942"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rc53fc90b01e84942"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rbe2f8eefcead4aa1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9210,7 +9210,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="287">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SatorImaging.TDoubles</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/SatorImaging.TDoubles</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/SatorImaging.TDoubles/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/sator-imaging/TDoubles</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tests</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-08-27T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F286"/>
+  <x:autoFilter ref="A1:F287"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rbe2f8eefcead4aa1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R0e1726e44ae84ced"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9242,7 +9242,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="288">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TrimItEasy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/TrimItEasy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/TrimItEasy/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/phongnguyend/TrimItEasy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EnhancementClass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-08-28T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F287"/>
+  <x:autoFilter ref="A1:F288"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R0e1726e44ae84ced"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rb4e291f50a89482e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rb4e291f50a89482e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Re143a16c91eb4805"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9274,7 +9274,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="289">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Najlot.Map.SourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Najlot.Map.SourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Najlot.Map.SourceGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/najlot/Map</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Mapper</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-08-29T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F288"/>
+  <x:autoFilter ref="A1:F289"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Re143a16c91eb4805"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R593db85c6d0042ad"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R593db85c6d0042ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R1b118b72a1af4496"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9306,7 +9306,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="290">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AOP.Logging.SourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/AOP.Logging.SourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/AOP.Logging.SourceGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/dborgards/aop.logging.net</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EnhancementClass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-08-30T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F289"/>
+  <x:autoFilter ref="A1:F290"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R1b118b72a1af4496"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rccdd929669cb41a8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9338,7 +9338,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="291">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MagicConstants</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/MagicConstants</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/MagicConstants/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/LieselThuriot/MagicConstants</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FilesToCode</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-09-04T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F290"/>
+  <x:autoFilter ref="A1:F291"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rccdd929669cb41a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R6cbe29be6b9f4803"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9370,7 +9370,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="292">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tenekon.MethodOverloads.SourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/Tenekon.MethodOverloads.SourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/Tenekon.MethodOverloads.SourceGenerator/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/tenekon/Tenekon.MethodOverloads.SourceGenerator</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EnhancementClass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-09-05T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F291"/>
+  <x:autoFilter ref="A1:F292"/>
 </x:worksheet>
 </file>
--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R6cbe29be6b9f4803"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rb924ed0efda7410c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/v2/rscg_examples_site/static/exports/RSCG.xlsx
+++ b/v2/rscg_examples_site/static/exports/RSCG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="Rb924ed0efda7410c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RSCG" sheetId="1" r:id="R2168b164440747b8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9402,7 +9402,39 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="293">
+      <x:c r="A" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">LayeredCraft.OptimizedEnums</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://ignatandrei.github.io/RSCG_Examples/v2/docs/LayeredCraft.OptimizedEnums</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://www.nuget.org/packages/LayeredCraft.OptimizedEnums/</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://github.com/layeredcraft/optimized-enums</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-09-06T00:00:00</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:F292"/>
+  <x:autoFilter ref="A1:F293"/>
 </x:worksheet>
 </file>